--- a/exports/导入差异_填写好的巡检结果_2026-06-09.xlsx
+++ b/exports/导入差异_填写好的巡检结果_2026-06-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,20 +434,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>楼栋</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>原因</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>变更内容</t>
         </is>
@@ -462,31 +457,18 @@
           <t>PLBD8C195CADB9</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>FH-001</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1号楼</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>状态: 待执行→已完成 | 检查日期: (空)→2026-06-09 | 结果: (空)→压力正常/标签完好；正常检查 | 照片数: 0→1</t>
-        </is>
-      </c>
+          <t>计划编号不存在</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,31 +479,18 @@
           <t>PL486C95CA38C4</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>FH-002</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1号楼</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>状态: 待执行→已完成 | 检查日期: (空)→2026-06-10 | 结果: (空)→压力正常；延期1天检查 | 照片数: 0→1</t>
-        </is>
-      </c>
+          <t>计划编号不存在</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -532,31 +501,18 @@
           <t>PL80CD126A08D8</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FH-003</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1号楼</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>状态: 待执行→有隐患 | 检查日期: (空)→2026-06-11 | 结果: (空)→压力不足；延期2天发现隐患 | 照片数: 0→2</t>
-        </is>
-      </c>
+          <t>计划编号不存在</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -568,18 +524,17 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>跳过</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>跳过</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>计划编号不存在</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -590,23 +545,18 @@
           <t>PLF3C1DE7AFC78</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FH-999</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>跳过</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>跳过</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>设备编号与计划不匹配</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>计划编号不存在</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -617,27 +567,18 @@
           <t>PL40CF83537F2E</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FH-005</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>跳过</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>跳过</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>检查日期格式错误</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>原始值=2026-13-40</t>
-        </is>
-      </c>
+          <t>计划编号不存在</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -648,31 +589,18 @@
           <t>PL5A398200ED19</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FH-006</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1号楼</t>
+          <t>跳过</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>状态: 待执行→已完成 | 检查日期: (空)→2026-06-09 | 结果: (空)→未填状态会推断；空状态推断</t>
-        </is>
-      </c>
+          <t>计划编号不存在</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
